--- a/ZonasEscolares/excels/LAMBAYEQUE-FERREÑAFE-FERREÑAFE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-FERREÑAFE-FERREÑAFE.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LAMBAYEQUE-FERREÑAFE-FERREÑAFE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-FERREÑAFE-FERREÑAFE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>101</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-6.64007</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.78879999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>353</v>
-      </c>
-      <c r="J2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-6.64007</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.7888</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>106 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-6.63128</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.78476999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>275</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-6.63128</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.78477</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>10057 JOSE MERCEDES ESTEVES CHICOMA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-6.639702</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.784688</v>
-      </c>
-      <c r="I4" t="n">
-        <v>400</v>
-      </c>
-      <c r="J4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-6.639702</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.784688</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>10058</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-6.64134</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.79155</v>
-      </c>
-      <c r="I5" t="n">
-        <v>515</v>
-      </c>
-      <c r="J5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-6.64134</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.79155</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>10059 JUAN GALO MUÑOZ PALACIOS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-6.63464</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.78864</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1159</v>
-      </c>
-      <c r="J6" t="n">
-        <v>43</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-6.63464</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.78864</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>10626 JOSE CESAR SOLIS CELIS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-6.64425</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.78852999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1016</v>
-      </c>
-      <c r="J7" t="n">
-        <v>44</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-6.64425</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.78853</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>MANUEL ANTONIO MESONES MURO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-6.63973</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.79189</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2098</v>
-      </c>
-      <c r="J8" t="n">
-        <v>82</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-6.63973</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.79189</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>11033 MARIO SAMAME BOGGIO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-6.631622</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.78550799999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>440</v>
-      </c>
-      <c r="J9" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-6.631622</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.785508</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>SANTA LUCIA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-6.64582</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.79001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1840</v>
-      </c>
-      <c r="J10" t="n">
-        <v>81</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-6.64582</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.79001</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>10056 HECTOR RENE LANEGRA ROMERO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-6.63199</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.78570999999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>532</v>
-      </c>
-      <c r="J11" t="n">
-        <v>29</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6.63199</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.78571</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>AUGUSTA LOPEZ ARENAS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-6.63936</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.78761</v>
-      </c>
-      <c r="I12" t="n">
-        <v>630</v>
-      </c>
-      <c r="J12" t="n">
-        <v>38</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-6.63936</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.78761</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>MARIA INMACULADA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-6.6381</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.78762999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>230</v>
-      </c>
-      <c r="J13" t="n">
-        <v>19</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-6.6381</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-79.78763</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>10084</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-6.236474</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.31639199999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>769</v>
-      </c>
-      <c r="J14" t="n">
-        <v>36</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-6.236474</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.316392</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>10083 INDOAMERICA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-6.278794</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.373341</v>
-      </c>
-      <c r="I15" t="n">
-        <v>270</v>
-      </c>
-      <c r="J15" t="n">
-        <v>15</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-6.278794</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.373341</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>10094 ROSA MURO GUEVARA DE BARRAGAN</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-6.645878</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-79.737905</v>
-      </c>
-      <c r="I16" t="n">
-        <v>269</v>
-      </c>
-      <c r="J16" t="n">
-        <v>16</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-6.645878</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.737905</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>11538</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-6.457151</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-79.665036</v>
-      </c>
-      <c r="I17" t="n">
-        <v>266</v>
-      </c>
-      <c r="J17" t="n">
-        <v>18</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-6.457151</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-79.665036</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>PERU BIRF</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-6.63824</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-79.79277999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1003</v>
-      </c>
-      <c r="J18" t="n">
-        <v>63</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-6.63824</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-79.79278</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>PEDRO RUIZ GALLO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-6.634641</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-79.787919</v>
-      </c>
-      <c r="I19" t="n">
-        <v>211</v>
-      </c>
-      <c r="J19" t="n">
-        <v>15</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-6.634641</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-79.787919</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>PEDRO RUIZ GALLO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-6.64004</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-79.78935</v>
-      </c>
-      <c r="I20" t="n">
-        <v>356</v>
-      </c>
-      <c r="J20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-6.64004</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-79.78935</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>AFUL FERREÑAFE</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-6.64141</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-79.78907</v>
-      </c>
-      <c r="I21" t="n">
-        <v>307</v>
-      </c>
-      <c r="J21" t="n">
-        <v>26</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-6.64141</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-79.78907</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>CHIQUIMUNDO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-6.639227</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-79.78804</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-6.639227</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-79.78804</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>OMEGA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-6.639227</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-79.78804</v>
-      </c>
-      <c r="I23" t="n">
-        <v>37</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-6.639227</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-79.78804</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LAMBAYEQUE-FERREÑAFE-FERREÑAFE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-FERREÑAFE-FERREÑAFE.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>281646</t>
+          <t>826020</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>CHIQUIMUNDO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.64007</t>
+          <t>-6.639227</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.7888</t>
+          <t>-79.78804</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>281670</t>
+          <t>282542</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10057 JOSE MERCEDES ESTEVES CHICOMA</t>
+          <t>10083 INDOAMERICA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.639702</t>
+          <t>-6.278794</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.784688</t>
+          <t>-79.373341</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>509475</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.64134</t>
+          <t>-6.634641</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.79155</t>
+          <t>-79.787919</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>281694</t>
+          <t>281646</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10059 JUAN GALO MUÑOZ PALACIOS</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.63464</t>
+          <t>-6.64007</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.78864</t>
+          <t>-79.7888</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>281707</t>
+          <t>283042</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10626 JOSE CESAR SOLIS CELIS</t>
+          <t>10094 ROSA MURO GUEVARA DE BARRAGAN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.64425</t>
+          <t>-6.645878</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.78853</t>
+          <t>-79.737905</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>269</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>281712</t>
+          <t>283400</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MANUEL ANTONIO MESONES MURO</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.63973</t>
+          <t>-6.457151</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.79189</t>
+          <t>-79.665036</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>281731</t>
+          <t>281854</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11033 MARIO SAMAME BOGGIO</t>
+          <t>MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.631622</t>
+          <t>-6.6381</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.785508</t>
+          <t>-79.78763</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>281745</t>
+          <t>281731</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SANTA LUCIA</t>
+          <t>11033 MARIO SAMAME BOGGIO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.64582</t>
+          <t>-6.631622</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.79001</t>
+          <t>-79.785508</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>440</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>281811</t>
+          <t>281670</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10056 HECTOR RENE LANEGRA ROMERO</t>
+          <t>10057 JOSE MERCEDES ESTEVES CHICOMA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.63199</t>
+          <t>-6.639702</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.78571</t>
+          <t>-79.784688</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>281849</t>
+          <t>586464</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AUGUSTA LOPEZ ARENAS</t>
+          <t>PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.63936</t>
+          <t>-6.64004</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.78761</t>
+          <t>-79.78935</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>356</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>281854</t>
+          <t>281689</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.6381</t>
+          <t>-6.64134</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.78763</t>
+          <t>-79.79155</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>515</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>282504</t>
+          <t>677204</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>AFUL FERREÑAFE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.236474</t>
+          <t>-6.64141</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.316392</t>
+          <t>-79.78907</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>282542</t>
+          <t>281811</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10083 INDOAMERICA</t>
+          <t>10056 HECTOR RENE LANEGRA ROMERO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.278794</t>
+          <t>-6.63199</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.373341</t>
+          <t>-79.78571</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>532</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>283042</t>
+          <t>864724</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10094 ROSA MURO GUEVARA DE BARRAGAN</t>
+          <t>OMEGA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.645878</t>
+          <t>-6.639227</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.737905</t>
+          <t>-79.78804</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>283400</t>
+          <t>282504</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.457151</t>
+          <t>-6.236474</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.665036</t>
+          <t>-79.316392</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>769</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>283476</t>
+          <t>281849</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PERU BIRF</t>
+          <t>AUGUSTA LOPEZ ARENAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.63824</t>
+          <t>-6.63936</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.79278</t>
+          <t>-79.78761</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>630</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>509475</t>
+          <t>281694</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PEDRO RUIZ GALLO</t>
+          <t>10059 JUAN GALO MUÑOZ PALACIOS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.634641</t>
+          <t>-6.63464</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.787919</t>
+          <t>-79.78864</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>586464</t>
+          <t>281707</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PEDRO RUIZ GALLO</t>
+          <t>10626 JOSE CESAR SOLIS CELIS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.64004</t>
+          <t>-6.64425</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.78935</t>
+          <t>-79.78853</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>677204</t>
+          <t>283476</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AFUL FERREÑAFE</t>
+          <t>PERU BIRF</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.64141</t>
+          <t>-6.63824</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.78907</t>
+          <t>-79.79278</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>826020</t>
+          <t>281745</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CHIQUIMUNDO</t>
+          <t>SANTA LUCIA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.639227</t>
+          <t>-6.64582</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.78804</t>
+          <t>-79.79001</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>864724</t>
+          <t>281712</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>OMEGA</t>
+          <t>MANUEL ANTONIO MESONES MURO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.639227</t>
+          <t>-6.63973</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.78804</t>
+          <t>-79.79189</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">

--- a/ZonasEscolares/excels/LAMBAYEQUE-FERREÑAFE-FERREÑAFE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-FERREÑAFE-FERREÑAFE.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>826020</t>
+          <t>864724</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CHIQUIMUNDO</t>
+          <t>OMEGA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>-6.639227</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>-79.78804</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>281651</t>
+          <t>826020</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>106 VIRGEN DE FATIMA</t>
+          <t>CHIQUIMUNDO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.63128</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.78477</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-6.639227</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.78804</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>282542</t>
+          <t>677204</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10083 INDOAMERICA</t>
+          <t>AFUL FERREÑAFE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.278794</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.373341</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-6.64141</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.78907</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>509475</t>
+          <t>586464</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -697,27 +697,27 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.634641</t>
+          <t>356</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.787919</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-6.64004</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.78935</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>281646</t>
+          <t>509475</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.64007</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.7888</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>-6.634641</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.787919</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>283042</t>
+          <t>283476</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10094 ROSA MURO GUEVARA DE BARRAGAN</t>
+          <t>PERU BIRF</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.645878</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.737905</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>-6.63824</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.79278</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -883,22 +883,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>-6.457151</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>-79.665036</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>281854</t>
+          <t>283042</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA</t>
+          <t>10094 ROSA MURO GUEVARA DE BARRAGAN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.6381</t>
+          <t>269</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.78763</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>-6.645878</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.737905</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>281731</t>
+          <t>282542</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11033 MARIO SAMAME BOGGIO</t>
+          <t>10083 INDOAMERICA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.631622</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.785508</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>-6.278794</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.373341</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>281670</t>
+          <t>282504</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10057 JOSE MERCEDES ESTEVES CHICOMA</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.639702</t>
+          <t>769</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.784688</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>-6.236474</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.316392</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>586464</t>
+          <t>281854</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PEDRO RUIZ GALLO</t>
+          <t>MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.64004</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.78935</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>-6.6381</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.78763</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>281849</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>AUGUSTA LOPEZ ARENAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.64134</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.79155</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>-6.63936</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-79.78761</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>677204</t>
+          <t>281811</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFUL FERREÑAFE</t>
+          <t>10056 HECTOR RENE LANEGRA ROMERO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.64141</t>
+          <t>532</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.78907</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>-6.63199</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-79.78571</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>281811</t>
+          <t>281745</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10056 HECTOR RENE LANEGRA ROMERO</t>
+          <t>SANTA LUCIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.63199</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.78571</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>-6.64582</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.79001</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>864724</t>
+          <t>281731</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OMEGA</t>
+          <t>11033 MARIO SAMAME BOGGIO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.639227</t>
+          <t>440</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.78804</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-6.631622</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-79.785508</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>282504</t>
+          <t>281712</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>MANUEL ANTONIO MESONES MURO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.236474</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.316392</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>-6.63973</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-79.79189</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>281849</t>
+          <t>281707</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AUGUSTA LOPEZ ARENAS</t>
+          <t>10626 JOSE CESAR SOLIS CELIS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.63936</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.78761</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>-6.64425</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.78853</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1565,22 +1565,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>-6.63464</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>-79.78864</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1159</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>281707</t>
+          <t>281689</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10626 JOSE CESAR SOLIS CELIS</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.64425</t>
+          <t>515</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.78853</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>-6.64134</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-79.79155</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>283476</t>
+          <t>281670</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PERU BIRF</t>
+          <t>10057 JOSE MERCEDES ESTEVES CHICOMA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.63824</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.79278</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>-6.639702</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-79.784688</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>281745</t>
+          <t>281651</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SANTA LUCIA</t>
+          <t>106 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.64582</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.79001</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>-6.63128</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>-79.78477</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>281712</t>
+          <t>281646</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MANUEL ANTONIO MESONES MURO</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.63973</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.79189</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>-6.64007</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>-79.7888</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">

--- a/ZonasEscolares/excels/LAMBAYEQUE-FERREÑAFE-FERREÑAFE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-FERREÑAFE-FERREÑAFE.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
